--- a/Stock_OneClick/history/scan_result_20260601_132301.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_132301.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -664,24 +664,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -733,24 +715,6 @@
       <c r="J4" t="n">
         <v>136.62</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -802,27 +766,15 @@
       <c r="J5" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -871,24 +823,6 @@
       <c r="J6" t="n">
         <v>72.75</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -940,24 +874,12 @@
       <c r="J7" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1009,24 +931,12 @@
       <c r="J8" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=-4.24%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1078,24 +988,6 @@
       <c r="J9" t="n">
         <v>323.39</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-0.16%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1147,24 +1039,12 @@
       <c r="J10" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1216,24 +1096,6 @@
       <c r="J11" t="n">
         <v>14.7</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1285,24 +1147,6 @@
       <c r="J12" t="n">
         <v>320.41</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1354,24 +1198,6 @@
       <c r="J13" t="n">
         <v>185.83</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1423,24 +1249,6 @@
       <c r="J14" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1492,24 +1300,6 @@
       <c r="J15" t="n">
         <v>27.15</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1561,24 +1351,6 @@
       <c r="J16" t="n">
         <v>50.55</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1630,24 +1402,6 @@
       <c r="J17" t="n">
         <v>905</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1699,24 +1453,6 @@
       <c r="J18" t="n">
         <v>11.02</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1768,24 +1504,6 @@
       <c r="J19" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1837,24 +1555,6 @@
       <c r="J20" t="n">
         <v>58.92</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1906,24 +1606,6 @@
       <c r="J21" t="n">
         <v>13.89</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1975,24 +1657,6 @@
       <c r="J22" t="n">
         <v>15.58</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2044,24 +1708,12 @@
       <c r="J23" s="5" t="n">
         <v>155.71</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2113,24 +1765,12 @@
       <c r="J24" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2182,24 +1822,6 @@
       <c r="J25" t="n">
         <v>163.09</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2251,24 +1873,6 @@
       <c r="J26" t="n">
         <v>54.5</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%</t>
@@ -2320,24 +1924,6 @@
       <c r="J27" t="n">
         <v>16.62</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2389,24 +1975,12 @@
       <c r="J28" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2458,24 +2032,6 @@
       <c r="J29" t="n">
         <v>47.59</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.10%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2527,24 +2083,6 @@
       <c r="J30" t="n">
         <v>400.08</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2596,24 +2134,6 @@
       <c r="J31" t="n">
         <v>950.54</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.49%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2665,24 +2185,12 @@
       <c r="J32" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2734,24 +2242,6 @@
       <c r="J33" t="n">
         <v>23.33</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2803,24 +2293,6 @@
       <c r="J34" t="n">
         <v>251.49</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%</t>
@@ -2872,24 +2344,6 @@
       <c r="J35" t="n">
         <v>145.02</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%</t>
@@ -2941,24 +2395,6 @@
       <c r="J36" t="n">
         <v>255.71</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -3010,24 +2446,12 @@
       <c r="J37" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3079,24 +2503,12 @@
       <c r="J38" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%</t>
@@ -3148,24 +2560,12 @@
       <c r="J39" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3217,24 +2617,6 @@
       <c r="J40" t="n">
         <v>459.97</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%</t>
@@ -3286,24 +2668,6 @@
       <c r="J41" t="n">
         <v>91.22</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%</t>
@@ -3355,24 +2719,12 @@
       <c r="J42" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3424,24 +2776,6 @@
       <c r="J43" t="n">
         <v>124.82</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3489,24 +2823,12 @@
       <c r="J44" s="5" t="n">
         <v>86.77</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-1.95%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3554,24 +2876,12 @@
       <c r="J45" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-6.73%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3623,24 +2933,12 @@
       <c r="J46" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3692,24 +2990,12 @@
       <c r="J47" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%</t>
@@ -3761,24 +3047,6 @@
       <c r="J48" t="n">
         <v>108.96</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%</t>
@@ -3830,24 +3098,12 @@
       <c r="J49" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%</t>
@@ -3899,24 +3155,6 @@
       <c r="J50" t="n">
         <v>83.78</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%</t>
@@ -3968,24 +3206,12 @@
       <c r="J51" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%</t>
@@ -4033,24 +3259,12 @@
       <c r="J52" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=0.18%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4098,24 +3312,12 @@
       <c r="J53" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-6.19%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4167,24 +3369,12 @@
       <c r="J54" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%</t>
@@ -4236,24 +3426,6 @@
       <c r="J55" t="n">
         <v>248.15</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.95%</t>
@@ -4305,24 +3477,6 @@
       <c r="J56" t="n">
         <v>273.51</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%</t>
@@ -4374,24 +3528,12 @@
       <c r="J57" s="5" t="n">
         <v>782.17</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4443,24 +3585,6 @@
       <c r="J58" t="n">
         <v>64.61</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%</t>
@@ -4508,24 +3632,12 @@
       <c r="J59" s="5" t="n">
         <v>1050.77</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-1.75%</t>
@@ -4577,24 +3689,12 @@
       <c r="J60" s="5" t="n">
         <v>147.14</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%</t>
@@ -4646,24 +3746,12 @@
       <c r="J61" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%</t>
@@ -4715,24 +3803,12 @@
       <c r="J62" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%</t>
@@ -4784,24 +3860,6 @@
       <c r="J63" t="n">
         <v>264.51</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%</t>
@@ -4853,24 +3911,12 @@
       <c r="J64" s="5" t="n">
         <v>139.79</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%</t>
@@ -4922,24 +3968,12 @@
       <c r="J65" s="5" t="n">
         <v>300.48</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4991,24 +4025,12 @@
       <c r="J66" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%</t>
@@ -5060,24 +4082,12 @@
       <c r="J67" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%</t>
@@ -5129,24 +4139,12 @@
       <c r="J68" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%</t>
@@ -5198,24 +4196,6 @@
       <c r="J69" t="n">
         <v>115.58</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5263,24 +4243,12 @@
       <c r="J70" s="5" t="n">
         <v>99.187</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=99.19; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5328,24 +4296,12 @@
       <c r="J71" s="5" t="n">
         <v>16.02</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=16.02; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5582,24 +4538,12 @@
       <c r="J83" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -5651,24 +4595,6 @@
       <c r="J84" t="n">
         <v>105.65</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5720,24 +4646,6 @@
       <c r="J85" t="n">
         <v>64.61</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5789,24 +4697,12 @@
       <c r="J86" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5858,24 +4754,12 @@
       <c r="J87" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5927,24 +4811,12 @@
       <c r="J88" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5996,24 +4868,12 @@
       <c r="J89" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -6065,24 +4925,12 @@
       <c r="J90" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%</t>
@@ -6103,7 +4951,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6130,24 +4977,6 @@
       <c r="J91" t="n">
         <v>91.03</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=0.43%</t>
@@ -6199,24 +5028,12 @@
       <c r="J92" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%</t>
@@ -6268,24 +5085,12 @@
       <c r="J93" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%</t>
@@ -6306,7 +5111,6 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6333,24 +5137,6 @@
       <c r="J94" t="n">
         <v>38.79</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-06-01; 相对D0=3.14%</t>
@@ -6402,24 +5188,6 @@
       <c r="J95" t="n">
         <v>403.88</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%</t>
@@ -6471,24 +5239,12 @@
       <c r="J96" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%</t>
@@ -6540,24 +5296,12 @@
       <c r="J97" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%</t>
@@ -6609,24 +5353,12 @@
       <c r="J98" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%</t>
@@ -6678,24 +5410,6 @@
       <c r="J99" t="n">
         <v>155.71</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%</t>
@@ -6747,24 +5461,12 @@
       <c r="J100" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%</t>
@@ -6816,24 +5518,6 @@
       <c r="J101" t="n">
         <v>265.7</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%</t>
@@ -6885,24 +5569,12 @@
       <c r="J102" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%</t>
@@ -6954,24 +5626,6 @@
       <c r="J103" t="n">
         <v>492.29</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%</t>
@@ -7023,24 +5677,12 @@
       <c r="J104" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%</t>
@@ -7092,24 +5734,12 @@
       <c r="J105" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%</t>
@@ -7161,24 +5791,6 @@
       <c r="J106" t="n">
         <v>273.51</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%</t>
@@ -7230,24 +5842,12 @@
       <c r="J107" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%</t>
@@ -7299,24 +5899,6 @@
       <c r="J108" t="n">
         <v>27.15</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%</t>
@@ -7368,24 +5950,6 @@
       <c r="J109" t="n">
         <v>109.33</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%</t>
@@ -7437,24 +6001,12 @@
       <c r="J110" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%</t>
@@ -7506,24 +6058,12 @@
       <c r="J111" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P111" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="5" t="n"/>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="5" t="n"/>
       <c r="Q111" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%</t>
@@ -7620,7 +6160,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7632,7 +6171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8125,9 +6664,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="21" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -8172,9 +6709,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="21" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8264,10 +6799,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8279,7 +6810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8562,7 +7093,6 @@
       <c r="J7" s="18" t="n">
         <v>-0.017458</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8644,7 +7174,6 @@
       <c r="J9" s="19" t="n">
         <v>0.16864</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8971,9 +7500,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B25" s="21" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9012,9 +7539,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="21" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -9053,9 +7578,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9094,9 +7617,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="21" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -9193,9 +7714,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9207,7 +7725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9331,7 +7849,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F4" s="12" t="n">
@@ -9509,9 +8027,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="21" t="n"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9544,9 +8060,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="21" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9579,9 +8093,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="21" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9614,9 +8126,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="21" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9653,9 +8163,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="21" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9688,9 +8196,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B20" s="21" t="n"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9723,9 +8229,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B21" s="21" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -9758,9 +8262,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B22" s="21" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -9793,9 +8295,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B23" s="21" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9912,7 +8412,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9924,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10123,7 +8622,6 @@
       <c r="F7" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -10239,7 +8737,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10268,7 +8765,6 @@
       <c r="F12" t="n">
         <v>15.58</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -10585,9 +9081,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -10614,9 +9108,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -10643,9 +9135,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="21" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -10672,9 +9162,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10701,9 +9189,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -10730,9 +9216,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10843,7 +9327,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11241,7 +9724,6 @@
       <c r="V4" t="n">
         <v>315</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.44; 4H分金=38.99</t>
@@ -11599,7 +10081,6 @@
       <c r="V8" t="n">
         <v>274.75</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.87; 4H分金=29.59</t>
@@ -11867,7 +10348,6 @@
       <c r="V11" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=133.86; Gann0=69.92; 段涨幅=91.45%</t>
@@ -11955,7 +10435,6 @@
       <c r="V12" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=178.91; Gann0=147.57; 段涨幅=21.24%</t>
@@ -12037,8 +10516,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>94</v>
       </c>
@@ -12129,7 +10606,6 @@
       <c r="V14" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-18; 1出价格=68.97; Gann0=61.71; 段涨幅=11.76%</t>
@@ -12217,7 +10693,6 @@
       <c r="V15" t="n">
         <v>73.73999786376953</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.65; 4H分金=39.11</t>
@@ -12305,7 +10780,6 @@
       <c r="V16" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=149.31; Gann0=122.00; 段涨幅=22.39%</t>
@@ -12393,7 +10867,6 @@
       <c r="V17" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.17; 4H分金=37.91</t>
@@ -12475,8 +10948,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
         <v>82</v>
       </c>
@@ -12657,7 +11128,6 @@
       <c r="V20" t="n">
         <v>409.6499938964844</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.92; 4H分金=50.49</t>
@@ -13143,7 +11613,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13549,8 +12019,6 @@
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="n">
         <v>91</v>
       </c>
@@ -13641,7 +12109,6 @@
       <c r="V31" t="n">
         <v>11.90999984741211</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.02; 4H分金=49.87</t>
@@ -13729,7 +12196,6 @@
       <c r="V32" t="n">
         <v>643</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=643.00; Gann0=594.81; 段涨幅=8.10%</t>
@@ -13817,7 +12283,6 @@
       <c r="V33" t="n">
         <v>643</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.60; 4H分金=32.16</t>
@@ -13905,7 +12370,6 @@
       <c r="V34" t="n">
         <v>24.5</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.29; 4H分金=49.04</t>
@@ -13993,7 +12457,6 @@
       <c r="V35" t="n">
         <v>134.1100006103516</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.14; 4H分金=41.50</t>
@@ -14075,8 +12538,6 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="n">
         <v>95</v>
       </c>
@@ -14347,7 +12808,6 @@
       <c r="V39" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=33.82; Gann0=17.50; 段涨幅=93.26%</t>
@@ -14705,7 +13165,6 @@
       <c r="V43" t="n">
         <v>56.84000015258789</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.79; 4H分金=45.24</t>
@@ -15063,7 +13522,6 @@
       <c r="V47" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.29; 4H分金=52.30</t>
@@ -15151,7 +13609,6 @@
       <c r="V48" t="n">
         <v>86.43000030517578</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.54; 4H分金=45.20</t>
@@ -15239,7 +13696,6 @@
       <c r="V49" t="n">
         <v>394.6300048828125</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.55; 4H分金=50.76</t>
@@ -15327,7 +13783,6 @@
       <c r="V50" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=445.60; Gann0=393.63; 段涨幅=13.20%</t>
@@ -15415,7 +13870,6 @@
       <c r="V51" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.10; 4H分金=24.03</t>
@@ -15503,7 +13957,6 @@
       <c r="V52" t="n">
         <v>13.93000030517578</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.48; 4H分金=47.96</t>
@@ -15585,8 +14038,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>86</v>
       </c>
@@ -15671,8 +14122,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
         <v>91</v>
       </c>
@@ -15763,7 +14212,6 @@
       <c r="V55" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.12; 4H分金=40.44</t>
@@ -15851,7 +14299,6 @@
       <c r="V56" t="n">
         <v>51.58000183105469</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.41; 4H分金=45.41</t>
@@ -16190,7 +14637,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -16239,7 +14685,6 @@
           <t>98 超巨</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -16294,7 +14739,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -16400,7 +14844,6 @@
       <c r="D6" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46170</v>
       </c>
@@ -17059,7 +15502,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -17171,7 +15613,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -17260,7 +15701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18433,7 +16874,6 @@
       <c r="P19" s="18" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -18555,7 +16995,6 @@
       <c r="P21" s="19" t="n">
         <v>0.084009</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22"/>
     <row r="23">
@@ -18748,9 +17187,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -18839,11 +17276,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18855,7 +17287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19016,24 +17448,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19085,24 +17505,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19154,24 +17562,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19223,24 +17619,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19292,24 +17676,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19361,24 +17727,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19430,24 +17784,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19499,24 +17841,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19568,24 +17892,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19637,24 +17949,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19706,24 +18006,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19775,24 +18063,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19844,24 +18120,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19913,24 +18171,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19982,24 +18222,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20051,24 +18273,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20120,24 +18330,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20189,24 +18387,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20258,24 +18438,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20512,24 +18680,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20574,11 +18730,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20590,7 +18741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21383,7 +19534,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -21489,7 +19640,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -21706,9 +19857,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21759,9 +19908,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21812,9 +19959,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21865,9 +20010,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="21" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21918,9 +20061,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -21971,9 +20112,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -22024,9 +20163,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22148,8 +20285,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
